--- a/docs/lexicon_data_entry_template.xlsx
+++ b/docs/lexicon_data_entry_template.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ابدأ هنا · START HERE" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEXICON · المصطلحات" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TROPES · الأنماط" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REFERENCE · المرجع" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXAMPLES · أمثلة حقيقية" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REFERENCE · المرجع" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -321,6 +322,57 @@
 </comments>
 </file>
 
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Guide</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>The POST the comment appeared under. Repeat it on every comment row from that post.
+This is the most important column in the sheet: the same comment can be hate on one post and harmless on another.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>post = judging the post itself. comment = judging a comment under it.
+One post with 5 comments = 6 rows.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>For a 'post' row, repeat the post text here. For a 'comment' row, the comment.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>hate / benign / ambiguous.
+ambiguous is a REAL answer — use it when you genuinely cannot tell. It is not counted as a mistake.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Why this is the right answer. Written for someone who was not there.
+For a hard case, say what makes it hard.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Two people should label the same items INDEPENDENTLY, without seeing each other's answer.
+This measures whether the definition is clear enough to apply consistently. If two experts disagree often, the problem is the definition, not the model.</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>yes = a case that only makes sense with the post context, or that a careless reader would get wrong.
+These are reported separately, because overall scores can look fine while every hard case is wrong.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -610,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B36"/>
+  <dimension ref="B2:B71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -654,21 +706,21 @@
     <row r="8" ht="20" customHeight="1">
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>القاعدة الأهم · The most important rule</t>
+          <t>أي ورقة أستخدم؟ · Which sheet do I use?</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>إذا كان بإمكان شخص أن يكتب هذه العبارة حرفياً في تعليق ← ورقة LEXICON</t>
+          <t>وجدت منشوراً على فيسبوك فيه خطاب كراهية، وتعليقات مسيئة تحته. ماذا أفعل؟</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>إذا كانت وصفاً لنمط أو سلوك ← ورقة TROPES</t>
+          <t>Found a Facebook post with hate speech and hateful comments under it. What now?</t>
         </is>
       </c>
     </row>
@@ -676,16 +728,16 @@
       <c r="B11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>If a person could type it word-for-word in a comment → LEXICON sheet.</t>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>→ EXAMPLES sheet. The whole post and all its comments go there, one row each.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>If it describes a pattern or behaviour → TROPES sheet.</t>
+          <t>ورقة EXAMPLES. المنشور وكل تعليقاته، صف لكل واحد.</t>
         </is>
       </c>
     </row>
@@ -693,64 +745,64 @@
       <c r="B14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>عبدة الشيطان  ← LEXICON  (people type this)</t>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>ثم اسأل: هل رأيت كلمة أو نمطاً جديداً غير موجود في القاموس؟</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>التمييز بالإجازات في الدوام  ← TROPES  (nobody types this sentence)</t>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Then ask: did it contain a word or pattern the dictionary does not have yet?</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr"/>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>لا تصحح الأخطاء الإملائية · Do NOT fix spelling mistakes</t>
+    <row r="18">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>a NEW word people type      → add ONE row to LEXICON</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>إذا كتب المشارك «الشبطان» بدل «الشيطان»، اتركها كما هي وضعها في عمود variants.</t>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>a NEW pattern or behaviour  → add ONE row to TROPES</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>People really type it that way online. A 'corrected' term stops matching real posts.</t>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>nothing new                 → EXAMPLES only. This is the normal case.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="2" t="inlineStr"/>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>الأعمدة البنفسجية تحتاج حكمك · Purple columns need YOUR judgement</t>
+    <row r="22">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>لا تُدخل كل منشور في LEXICON. القاموس يحتوي على الكلمات، وليس المنشورات.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>لا توجد في الملفات الأصلية — أنت من يقررها. اقرأ التعليق على كل عمود.</t>
+          <t>Do NOT put every post into LEXICON. The dictionary holds words, not posts.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>These are not in the source files. You decide them. Read each column's note.</t>
+          <t>You will add a few LEXICON rows a week. You will add EXAMPLES rows constantly.</t>
         </is>
       </c>
     </row>
@@ -760,67 +812,280 @@
     <row r="26" ht="20" customHeight="1">
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>الأعمدة الحمراء إلزامية · Red columns are required</t>
+          <t>الفرق بين الأوراق · The difference</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>الصف الذي ينقصه أحدها سيُرفض عند الاستيراد · A row missing one of these is rejected on import.</t>
+          <t>LEXICON + TROPES = ما الذي يبحث عنه النظام  · WHAT the system looks for</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>الصفوف الرمادية أمثلة · Grey rows are examples</t>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>EXAMPLES = ما هو الجواب الصحيح على محتوى حقيقي · WHAT the right answer is</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Without EXAMPLES there is no way to know whether the system actually works.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>مأخوذة من بياناتكم الحقيقية. احذفوها قبل التسليم أو اتركوها — المستورد يتجاهلها.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Taken from your real data. Delete them before hand-off, or leave them — the importer skips them.</t>
+      <c r="B30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>القاعدة الأهم · LEXICON or TROPES?</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>سؤال شائع · A question that comes up</t>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>إذا كان بإمكان شخص أن يكتب هذه العبارة حرفياً في تعليق ← ورقة LEXICON</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>إذا كانت وصفاً لنمط أو سلوك ← ورقة TROPES</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>مصطلح واحد يُستخدم ضد أكثر من فئة؟ صف واحد فقط، واكتب الفئات مفصولة بفاصلة.</t>
-        </is>
-      </c>
+      <c r="B34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>One term used against several groups? ONE row, with the groups comma-separated.</t>
+          <t>If a person could type it word-for-word in a comment → LEXICON sheet.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>If it describes a pattern or behaviour → TROPES sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>عبدة الشيطان  ← LEXICON  (people type this)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>التمييز بالإجازات في الدوام  ← TROPES  (nobody types this sentence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>منشور واحد = عدة صفوف · One post = several rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>منشور فيه ٥ تعليقات = ٦ صفوف: صف للمنشور، وصف لكل تعليق.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>A post with 5 comments = 6 rows. One for the post, one per comment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Repeat the post text on every comment row — the same comment can be hate under</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>one post and completely harmless under another. That context IS the judgement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>سجّل التعليقات البريئة أيضاً · Record the harmless comments too</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>لا تسجل المسيء فقط. التعليقات العادية هي ما يقيس الإنذارات الكاذبة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Do not record only the hateful ones. The ordinary comments are what measure</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>false alarms — a system judged only on hate speech looks perfect while flagging</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>everyone. Record the whole thread as you found it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>لا تصحح الأخطاء الإملائية · Do NOT fix spelling mistakes</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>إذا كتب المشارك «الشبطان» بدل «الشيطان»، اتركها كما هي وضعها في عمود variants.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>People really type it that way online. A 'corrected' term stops matching real posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>الأعمدة البنفسجية تحتاج حكمك · Purple columns need YOUR judgement</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>لا توجد في الملفات الأصلية — أنت من يقررها. اقرأ التعليق على كل عمود.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>These are not in the source files. You decide them. Read each column's note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>الأعمدة الحمراء إلزامية · Red columns are required</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>الصف الذي ينقصه أحدها سيُرفض عند الاستيراد · A row missing one of these is rejected on import.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>الصفوف الرمادية أمثلة · Grey rows are examples</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>مأخوذة من بياناتكم الحقيقية. احذفوها قبل التسليم أو اتركوها — المستورد يتجاهلها.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Taken from your real data. Delete them before hand-off, or leave them — the importer skips them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>سؤال شائع · A question that comes up</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>مصطلح واحد يُستخدم ضد أكثر من فئة؟ صف واحد فقط، واكتب الفئات مفصولة بفاصلة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>One term used against several groups? ONE row, with the groups comma-separated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Two rows drift apart when someone edits only one of them.</t>
         </is>
@@ -1245,7 +1510,7 @@
       <formula1>"ar,ku"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="Pick a value from the list." type="list">
-      <formula1>"slur,threat,dehumanization,incitement"</formula1>
+      <formula1>"slur,mockery,authenticity_denial,collective_accusation,disloyalty,foreignness,delegitimization,dehumanization,exclusion_call,incitement,threat,counter_speech,news_reporting"</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="Pick a value from the list." type="list">
       <formula1>"yes,no"</formula1>
@@ -1566,6 +1831,542 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="46" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>الرابط
+post_url</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>نص المنشور
+parent_post_text *</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>نوع الصف
+row_type *</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>النص المراد تقييمه
+comment_text *</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>الفئة المستهدفة
+target_group</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>اللغة
+dialect</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>الحكم
+label *</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>النوع
+category</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>الخطورة ١-١٠
+severity</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>لماذا؟ (الآلية)
+why — the mechanism *</t>
+        </is>
+      </c>
+      <c r="K1" s="6" t="inlineStr">
+        <is>
+          <t>النمط
+demonstrates_trope</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>المقيّم ١
+annotator_1</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>المقيّم ٢
+annotator_2</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>حالة صعبة؟
+hard_case</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>https://facebook.com/example/posts/1</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>مراسم دينية إيزيدية في معبد لالش</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>مراسم دينية إيزيدية في معبد لالش</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>yazidi</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>iraqi</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr"/>
+      <c r="I2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>EXAMPLE — the post itself is a neutral description of a ceremony</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr"/>
+      <c r="L2" s="8" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="N2" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>https://facebook.com/example/posts/1</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>مراسم دينية إيزيدية في معبد لالش</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>اعوذ بالله من الشيطان الرجيم</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>yazidi</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>iraqi</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>hate</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>dehumanization</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>EXAMPLE — the pious phrase is AIMED AT Yazidi religious practice, which invokes the devil-worship libel. Any phrase invoking the devil against this community works the same way</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>Devil-worship libel</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>hate</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>hate</t>
+        </is>
+      </c>
+      <c r="N3" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>https://facebook.com/example/posts/1</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>مراسم دينية إيزيدية في معبد لالش</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>عبدة الشيطان كلهم</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>yazidi</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>iraqi</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>hate</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>dehumanization</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>EXAMPLE — explicit slur; hateful with or without the post context</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>Devil-worship libel</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>hate</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>hate</t>
+        </is>
+      </c>
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>https://facebook.com/example/posts/1</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>مراسم دينية إيزيدية في معبد لالش</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>الإيزيديون ليسوا عبدة الشيطان، هذا افتراء</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>yazidi</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>iraqi</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>counter_speech</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>EXAMPLE — quotes the libel in order to REFUTE it. Negation reverses the meaning; flagging this attacks a defender of the community</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>Devil-worship libel</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="N5" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>https://facebook.com/example/posts/1</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>مراسم دينية إيزيدية في معبد لالش</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>شكرا على المعلومات</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>yazidi</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>iraqi</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>EXAMPLE — ordinary comment. The clean ones matter: they measure false alarms</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr"/>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>https://facebook.com/other/posts/9</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>شاهدوا هذا الثعبان الضخم في الحديقة</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>اعوذ بالله من الشيطان الرجيم</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>iraqi</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>EXAMPLE — THE PAIR. Same words as row 3, but the post concerns a snake, so the phrase is ordinary piety. The MECHANISM is that the trope needs the group in context</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>Devil-worship libel</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="7">
+    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="Pick a value from the list." type="list">
+      <formula1>"post,comment"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="Pick a value from the list." type="list">
+      <formula1>"hate,benign,ambiguous"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="Pick a value from the list." type="list">
+      <formula1>"slur,mockery,authenticity_denial,collective_accusation,disloyalty,foreignness,delegitimization,dehumanization,exclusion_call,incitement,threat,counter_speech,news_reporting,counter_speech,news_reporting"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="Pick a value from the list." type="list">
+      <formula1>"hate,benign,ambiguous"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="Pick a value from the list." type="list">
+      <formula1>"hate,benign,ambiguous"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="Pick a value from the list." type="list">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="Pick a value from the list." type="list">
+      <formula1>"yazidi,christian-iraqi,shabak,kakai,sabian-mandaean,turkmen-iraqi,faili-kurd,bahai,kurdish"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/docs/lexicon_data_entry_template.xlsx
+++ b/docs/lexicon_data_entry_template.xlsx
@@ -1510,7 +1510,7 @@
       <formula1>"ar,ku"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="Pick a value from the list." type="list">
-      <formula1>"slur,mockery,authenticity_denial,collective_accusation,disloyalty,foreignness,delegitimization,dehumanization,exclusion_call,incitement,threat,counter_speech,news_reporting"</formula1>
+      <formula1>"mockery,authenticity_denial,collective_accusation,slur,incitement,foreignness,disloyalty,exclusion_call,delegitimization,dehumanization,threat,counter_speech,news_reporting"</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="Pick a value from the list." type="list">
       <formula1>"yes,no"</formula1>
@@ -2341,7 +2341,7 @@
       <formula1>"hate,benign,ambiguous"</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="Pick a value from the list." type="list">
-      <formula1>"slur,mockery,authenticity_denial,collective_accusation,disloyalty,foreignness,delegitimization,dehumanization,exclusion_call,incitement,threat,counter_speech,news_reporting,counter_speech,news_reporting"</formula1>
+      <formula1>"mockery,authenticity_denial,collective_accusation,slur,incitement,foreignness,disloyalty,exclusion_call,delegitimization,dehumanization,threat,counter_speech,news_reporting,counter_speech,news_reporting"</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="Pick a value from the list." type="list">
       <formula1>"hate,benign,ambiguous"</formula1>
